--- a/equipe/Hélio_Medina.xlsx
+++ b/equipe/Hélio_Medina.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SuporteLead\Desktop\dashboard_analytics\equipe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E703B552-D37B-44E0-AB21-1B8B09F012EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D26B2E-F1B2-4360-8A4C-AA36E1A5E95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{28FD2BDB-A87A-4B85-B83E-1AF1E0432417}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t xml:space="preserve">Quarter </t>
   </si>
@@ -826,19 +826,45 @@
       <c r="B4" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="10"/>
-      <c r="O4" s="11"/>
+      <c r="C4" s="5">
+        <v>14</v>
+      </c>
+      <c r="D4" s="5">
+        <v>31</v>
+      </c>
+      <c r="E4" s="6">
+        <v>20</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="6">
+        <v>3</v>
+      </c>
+      <c r="H4" s="6">
+        <v>20</v>
+      </c>
+      <c r="I4" s="8">
+        <v>6.67</v>
+      </c>
+      <c r="J4" s="9">
+        <v>0</v>
+      </c>
+      <c r="K4" s="9">
+        <v>0</v>
+      </c>
+      <c r="L4" s="9">
+        <v>0</v>
+      </c>
+      <c r="M4" s="9">
+        <v>0</v>
+      </c>
+      <c r="N4" s="10">
+        <v>0</v>
+      </c>
+      <c r="O4" s="11">
+        <v>0</v>
+      </c>
       <c r="P4" s="5"/>
       <c r="R4" t="s">
         <v>35</v>

--- a/equipe/Hélio_Medina.xlsx
+++ b/equipe/Hélio_Medina.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SuporteLead\Desktop\dashboard_analytics\equipe\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SuporteLead\Desktop\dell-analytics-pro\equipe\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29D26B2E-F1B2-4360-8A4C-AA36E1A5E95C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF65F2A6-0335-4861-AF48-062CAEB42ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{28FD2BDB-A87A-4B85-B83E-1AF1E0432417}"/>
   </bookViews>
@@ -754,7 +754,7 @@
         <v>0</v>
       </c>
       <c r="M2" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" s="10">
         <v>0</v>
